--- a/data.mn/public/datasets/government-balance.xlsx
+++ b/data.mn/public/datasets/government-balance.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1275,4 +1276,874 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>утга</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1921</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1927</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1932</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1937</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1939</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B23" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B24" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1944</v>
+      </c>
+      <c r="B25" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1945</v>
+      </c>
+      <c r="B26" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1946</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-19.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B33" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B34" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-14.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B44" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B45" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B46" t="n">
+        <v>75.90000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B47" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B48" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B49" t="n">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B51" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B52" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80.40000000000001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B54" t="n">
+        <v>147.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B55" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B56" t="n">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B57" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B58" t="n">
+        <v>178.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B59" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B60" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B61" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B63" t="n">
+        <v>72.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B64" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-587.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B66" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B67" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B68" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B70" t="n">
+        <v>-160.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B71" t="n">
+        <v>-318.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B72" t="n">
+        <v>-1720.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B73" t="n">
+        <v>464.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B74" t="n">
+        <v>453.7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B75" t="n">
+        <v>-9971.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B76" t="n">
+        <v>12415.8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B77" t="n">
+        <v>546.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B78" t="n">
+        <v>-65120.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B79" t="n">
+        <v>-102203.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B80" t="n">
+        <v>-95189.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B81" t="n">
+        <v>-86836.60000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B82" t="n">
+        <v>-50440.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B83" t="n">
+        <v>-71590.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B84" t="n">
+        <v>-61882</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B85" t="n">
+        <v>-39372.8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B86" t="n">
+        <v>73261.10000000001</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B87" t="n">
+        <v>123401.8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B88" t="n">
+        <v>133178.4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B89" t="n">
+        <v>-296404.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B90" t="n">
+        <v>-342634.1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B91" t="n">
+        <v>41779</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B92" t="n">
+        <v>-769861.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B93" t="n">
+        <v>-1136628.6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B94" t="n">
+        <v>-224618.7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B95" t="n">
+        <v>-867959.1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B96" t="n">
+        <v>-1156909.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B97" t="n">
+        <v>-3660289.1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B98" t="n">
+        <v>-1742456.9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B99" t="n">
+        <v>27859.3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B100" t="n">
+        <v>-756190.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B101" t="n">
+        <v>-4440434.8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B102" t="n">
+        <v>-2919009.2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B103" t="n">
+        <v>-1032732.6</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B104" t="n">
+        <v>785889.8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B105" t="n">
+        <v>-920248.3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B106" t="n">
+        <v>-1231538.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/government-balance.xlsx
+++ b/data.mn/public/datasets/government-balance.xlsx
@@ -1270,7 +1270,7 @@
         <v>2025</v>
       </c>
       <c r="B106" t="n">
-        <v>-1231538.2</v>
+        <v>-1027869.3</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2140,7 @@
         <v>2025</v>
       </c>
       <c r="B106" t="n">
-        <v>-1231538.2</v>
+        <v>-1027869.3</v>
       </c>
     </row>
   </sheetData>
